--- a/jogos_2024-10-03.xlsx
+++ b/jogos_2024-10-03.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
         <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AD3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['34']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45568.33333333334</v>
@@ -891,119 +891,119 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
         <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
         <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Y4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['24', '84']</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.71</v>
+        <v>1.62</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45568.33333333334</v>
@@ -1020,32 +1020,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
         <v>1.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['24', '84']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.95</v>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.77</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.73</v>
+        <v>2.71</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45568.33333333334</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['75', '90+2']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45568.45833333334</v>
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
         <v>2.38</v>
@@ -1716,19 +1716,19 @@
         <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
         <v>1.09</v>
@@ -1737,34 +1737,34 @@
         <v>1.51</v>
       </c>
       <c r="X10" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['15', '67']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1774,7 +1774,7 @@
         <v>1.93</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AJ10" t="n">
         <v>3.75</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1819,10 +1819,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['75', '90+2']</t>
+          <t>['15', '67']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45568.45833333334</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.89</v>
+        <v>5.68</v>
       </c>
       <c r="M16" t="n">
-        <v>3.68</v>
+        <v>4.71</v>
       </c>
       <c r="N16" t="n">
-        <v>3.71</v>
+        <v>1.46</v>
       </c>
       <c r="O16" t="n">
-        <v>2.49</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.08</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>3.95</v>
+        <v>5.18</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.84</v>
+        <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['4', '82']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['74', '90+14']</t>
+          <t>['50', '89']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>1.12</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45568.625</v>
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.68</v>
+        <v>1.89</v>
       </c>
       <c r="M17" t="n">
-        <v>4.71</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>1.46</v>
+        <v>3.71</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>2.49</v>
       </c>
       <c r="P17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['4', '82']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['74', '90+14']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['90+5']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['50', '89']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.42</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45568.625</v>
